--- a/tests/v1/fixtures/office6m/2026-10/bank_statements/TCB_HOLD_USD_2026-10_mtd.xlsx
+++ b/tests/v1/fixtures/office6m/2026-10/bank_statements/TCB_HOLD_USD_2026-10_mtd.xlsx
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>198829.25</v>
+        <v>202809.25</v>
       </c>
       <c r="E2" t="n">
-        <v>1059.49</v>
+        <v>-2920.51</v>
       </c>
       <c r="F2" t="n">
         <v>199888.74</v>
